--- a/EXCEL/Figur3_trs_split.xlsx
+++ b/EXCEL/Figur3_trs_split.xlsx
@@ -12018,7 +12018,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Kørsel 7.4.2026 10.15.33</t>
+          <t>Kørsel 7.4.2026 10.47.28</t>
         </is>
       </c>
     </row>
@@ -23776,7 +23776,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Kørsel 7.4.2026 10.15.36</t>
+          <t>Kørsel 7.4.2026 10.47.31</t>
         </is>
       </c>
     </row>
@@ -35774,7 +35774,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Kørsel 7.4.2026 10.15.39</t>
+          <t>Kørsel 7.4.2026 10.47.34</t>
         </is>
       </c>
     </row>
